--- a/hardware/docs/fabbit_bom.xlsx
+++ b/hardware/docs/fabbit_bom.xlsx
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>стальная стойка, крепление мезонина</t>
+          <t>стальная стойка, крепление модуля аналога, 4 точки</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
@@ -7687,7 +7687,7 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,5×47×60 мм</t>
+          <t>9,0×40×70 мм</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -7697,7 +7697,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>типоразмер 954760 (LP954760), Li-pol 1S, около 3000 мА·ч; плата защиты на ток разряда ≥ 2,8 А; производитель любой; провода к разъёму XH-3</t>
+          <t>типоразмер 904070 (LP904070), Li-pol 1S, 2800 мА·ч; плата защиты на ток разряда ≥ 2,8 А; производитель любой; провода к разъёму XH-3</t>
         </is>
       </c>
     </row>
